--- a/Assets/Editor/ExcelData/MatchDropData.xlsx
+++ b/Assets/Editor/ExcelData/MatchDropData.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SHINZI_Games_InternshipTest\Assets\Editor\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B5737F-CDF7-416F-A6F9-2DB88176B3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE15F75E-0A77-4A3C-96F2-03E9F38E7C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="WeaponData" sheetId="1" r:id="rId1"/>
+    <sheet name="MatchDropData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,64 +39,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>Range</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Melee</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>야구방망이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>총</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>폭탄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Throw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
   <si>
     <t>weaponId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>weaponType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>weaponName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>damage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attackCooldawn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>range</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>prefabAddressable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iconAddressable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Gun</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -106,6 +54,26 @@
   </si>
   <si>
     <t>Boom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropListId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DropList_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DropList_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DropList_3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -490,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A09DDB1-B5FD-4E66-B653-801C3E995E61}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -502,90 +470,103 @@
     <col min="8" max="8" width="43.3125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>50</v>
-      </c>
-      <c r="E2">
-        <v>1.5</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="C8">
         <v>3</v>
       </c>
-      <c r="D3">
-        <v>15</v>
-      </c>
-      <c r="E3">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
         <v>3</v>
       </c>
-      <c r="F3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.6">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C9">
         <v>4</v>
-      </c>
-      <c r="D4">
-        <v>30</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Editor/ExcelData/MatchDropData.xlsx
+++ b/Assets/Editor/ExcelData/MatchDropData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SHINZI_Games_InternshipTest\Assets\Editor\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE15F75E-0A77-4A3C-96F2-03E9F38E7C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C48E999-A7B9-4976-8A0D-D590F904D8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
   </bookViews>
   <sheets>
     <sheet name="MatchDropData" sheetId="1" r:id="rId1"/>
@@ -39,20 +39,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="12">
   <si>
     <t>weaponId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Gun</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bat</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Boom</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -74,6 +66,26 @@
   </si>
   <si>
     <t>DropList_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arrow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Melee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hammer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -458,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A09DDB1-B5FD-4E66-B653-801C3E995E61}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -472,13 +484,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.6">
@@ -486,10 +498,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2">
         <v>2</v>
-      </c>
-      <c r="C2">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.6">
@@ -497,7 +509,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -505,21 +517,21 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -527,10 +539,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -538,38 +550,74 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
-        <v>1</v>
-      </c>
       <c r="C8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C11">
         <v>3</v>
       </c>
-      <c r="C9">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A12" t="s">
         <v>4</v>
       </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C12">
+    <sortCondition descending="1" ref="A2:A12"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/Editor/ExcelData/MatchDropData.xlsx
+++ b/Assets/Editor/ExcelData/MatchDropData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SHINZI_Games_InternshipTest\Assets\Editor\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C48E999-A7B9-4976-8A0D-D590F904D8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E3A726-6B49-480D-9943-B1B2840054E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
   </bookViews>
   <sheets>
     <sheet name="MatchDropData" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="11">
   <si>
     <t>weaponId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -73,19 +73,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Arrow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Melee</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Hammer</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Shield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bow</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -498,7 +494,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -520,7 +516,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -531,7 +527,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -564,7 +560,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -575,7 +571,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -597,7 +593,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -608,7 +604,7 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12">
         <v>3</v>

--- a/Assets/Editor/ExcelData/MatchDropData.xlsx
+++ b/Assets/Editor/ExcelData/MatchDropData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SHINZI_Games_InternshipTest\Assets\Editor\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E3A726-6B49-480D-9943-B1B2840054E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1633B4C-04BF-417F-9D49-D754D44E0CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
   </bookViews>
   <sheets>
     <sheet name="MatchDropData" sheetId="1" r:id="rId1"/>
@@ -39,13 +39,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="10">
   <si>
     <t>weaponId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Boom</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -466,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A09DDB1-B5FD-4E66-B653-801C3E995E61}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -480,21 +476,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -502,10 +498,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -513,10 +509,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -524,10 +520,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -535,21 +531,21 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
       <c r="C6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -557,56 +553,45 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.6">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12">
         <v>3</v>
       </c>
     </row>

--- a/Assets/Editor/ExcelData/MatchDropData.xlsx
+++ b/Assets/Editor/ExcelData/MatchDropData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SHINZI_Games_InternshipTest\Assets\Editor\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1633B4C-04BF-417F-9D49-D754D44E0CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645D13F4-3676-41A3-AD3E-8E27F346AAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
   </bookViews>
@@ -493,7 +493,7 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.6">

--- a/Assets/Editor/ExcelData/MatchDropData.xlsx
+++ b/Assets/Editor/ExcelData/MatchDropData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\SHINZI_Games_InternshipTest\Assets\Editor\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645D13F4-3676-41A3-AD3E-8E27F346AAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1633B4C-04BF-417F-9D49-D754D44E0CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26BA0CAA-DEB9-4337-88BD-7920261670E1}"/>
   </bookViews>
@@ -493,7 +493,7 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.6">
